--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Checking_Reconciliation.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Checking_Reconciliation.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -588,7 +588,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
